--- a/JsonConverter/ExcelFiles/Active.xlsx
+++ b/JsonConverter/ExcelFiles/Active.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\개발\포크\SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD03FB6F-246C-40A0-9714-16B0ACA96B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28485" yWindow="1965" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28485" yWindow="1965" windowWidth="28185" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Active" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -116,13 +115,43 @@
   </si>
   <si>
     <t>TexturePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>active_05</t>
+  </si>
+  <si>
+    <t>active_06</t>
+  </si>
+  <si>
+    <t>Farming</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food Supply</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 아이템 ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Resources_01,Item_Resources_02,Item_Resources_03,Item_Resources_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Food_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4">
     <font>
       <sz val="10"/>
@@ -454,22 +483,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G997"/>
+  <dimension ref="A1:H997"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="50.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -480,15 +510,18 @@
         <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -499,19 +532,22 @@
         <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -522,19 +558,22 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -544,16 +583,17 @@
       <c r="C4" s="4">
         <v>5</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4"/>
+      <c r="E4" s="3">
         <v>100</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>3</v>
       </c>
-      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -563,16 +603,17 @@
       <c r="C5" s="4">
         <v>5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4"/>
+      <c r="E5" s="3">
         <v>100</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>3</v>
       </c>
-      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -582,16 +623,17 @@
       <c r="C6" s="4">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4"/>
+      <c r="E6" s="3">
         <v>100</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>3</v>
       </c>
-      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -601,34 +643,53 @@
       <c r="C7" s="3">
         <v>5</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
         <v>100</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>3</v>
       </c>
-      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -636,8 +697,9 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -645,8 +707,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -654,8 +717,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -663,8 +727,9 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -672,8 +737,9 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -681,8 +747,9 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -690,8 +757,9 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -699,8 +767,9 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -708,8 +777,9 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -717,8 +787,9 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -726,8 +797,9 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -735,8 +807,9 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -744,8 +817,9 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -753,8 +827,9 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -762,8 +837,9 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -771,8 +847,9 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -780,8 +857,9 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -789,8 +867,9 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -798,8 +877,9 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -807,8 +887,9 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -816,8 +897,9 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -825,8 +907,9 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -834,6 +917,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -1803,6 +1887,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Active.xlsx
+++ b/JsonConverter/ExcelFiles/Active.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Id</t>
   </si>
@@ -145,6 +145,16 @@
   </si>
   <si>
     <t>ItemId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해금 날짜</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>UnlockDate</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -152,7 +162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -178,8 +188,21 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,8 +239,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2F2DB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -240,13 +273,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -269,6 +330,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -487,219 +555,247 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H997"/>
+  <dimension ref="A1:I997"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="50.7109375" customWidth="1"/>
+    <col min="2" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="13">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
         <v>5</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3">
         <v>100</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>3</v>
       </c>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="13">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
         <v>5</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="3">
         <v>100</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>3</v>
       </c>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="14">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
         <v>5</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3">
+      <c r="E6" s="4"/>
+      <c r="F6" s="3">
         <v>100</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>3</v>
       </c>
-      <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="14">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
         <v>5</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <v>100</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>3</v>
       </c>
-      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="14">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4">
         <v>5</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="14">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -708,28 +804,30 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -738,8 +836,9 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -748,8 +847,9 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -758,8 +858,9 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -768,8 +869,9 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -778,8 +880,9 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -788,8 +891,9 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -798,8 +902,9 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -808,8 +913,9 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -818,8 +924,9 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -828,8 +935,9 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -838,8 +946,9 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -848,8 +957,9 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -858,8 +968,9 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -868,8 +979,9 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -878,8 +990,9 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -888,8 +1001,9 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -898,8 +1012,9 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -908,8 +1023,9 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -918,6 +1034,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Active.xlsx
+++ b/JsonConverter/ExcelFiles/Active.xlsx
@@ -1,36 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30317"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\개발\포크\SunnyHoGaming\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85867b8a770c3dbd/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA3B8E5E-788F-4A5B-870E-F453D8F43C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28485" yWindow="1965" windowWidth="28185" windowHeight="12795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Active" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
+    <t>고유 ID</t>
+  </si>
+  <si>
+    <t>활동 이름</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해금 날짜</t>
+  </si>
+  <si>
+    <t>소요 시간(hour)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 아이템 ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원 필요량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간당 감소 수치(100%기준)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(name)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>고유 ID</t>
-  </si>
-  <si>
-    <t>(name)</t>
+    <t>Name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockDate</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -38,6 +101,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>ItemId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>ResourcesCost</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -46,7 +113,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>자원 필요량</t>
+    <t>TexturePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoundPath</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -54,114 +125,60 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>산소 공급기 수리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>active_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>발전기 수리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>active_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>온도 제어장치 수리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>active_04</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>활동 이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Oxygen Supply</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Supply</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Temperature Control</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Route Control</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간당 감소 수치(100%기준)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoundPath</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>소요 시간(hour)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TexturePath</t>
+    <t>항로제어 장치 수리</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>active_05</t>
   </si>
   <si>
+    <t>수리 재료 수급</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Resources_01,Item_Resources_02,Item_Resources_03,Item_Resources_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>active_06</t>
   </si>
   <si>
-    <t>Farming</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Food Supply</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>획득 아이템 ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Resources_01,Item_Resources_02,Item_Resources_03,Item_Resources_04</t>
+    <t>식량 수급</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Item_Food_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해금 날짜</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>UnlockDate</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -551,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -569,82 +586,82 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>33</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>21</v>
@@ -652,10 +669,10 @@
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" s="13">
         <v>1</v>
@@ -675,10 +692,10 @@
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5" s="13">
         <v>1</v>
@@ -698,10 +715,10 @@
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C6" s="14">
         <v>1</v>
@@ -721,10 +738,10 @@
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C7" s="14">
         <v>1</v>
@@ -744,10 +761,10 @@
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="14">
         <v>3</v>
@@ -756,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -765,10 +782,10 @@
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C9" s="14">
         <v>4</v>
@@ -777,7 +794,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
